--- a/光伏配储项目/电价数据/2026/越王山站.xlsx
+++ b/光伏配储项目/电价数据/2026/越王山站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.48439</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38452</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.7554500000000001</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.5426599999999999</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.5570000000000001</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.48541</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.42483</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.43952</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.41697</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.40942</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.40814</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.39783</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.38793</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.37686</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.39112</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.40114</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.38262</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.40694</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.38379</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.40411</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.4136</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.40326</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.42998</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.47274</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.3874</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.34467</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.36394</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32245</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.15239</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.23393</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.00696</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.21558</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>-0.02268</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.07612999999999999</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.03919</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.15695</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.16072</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.14633</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.09779</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>-0.01473</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.38597</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.5139400000000001</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.53623</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.73393</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.12103</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.3948</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.1849</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43154</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.66122</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.86356</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.47219</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.19461</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.43504</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.29485</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.9892799999999999</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.28007</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.50168</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.43487</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.6812</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.7314400000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.08948</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.95786</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8923099999999999</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.8003899999999999</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.76124</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.51476</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.48343</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.46492</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41764</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42753</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7170299999999999</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.88905</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.9418500000000001</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.50247</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52479</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50936</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.5095</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.49149</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.40247</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47299</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.38034</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38346</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.42774</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33721</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.36536</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36538</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.4063</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.39272</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>1.14885</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>1.00805</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>1.07037</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.49126</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.48741</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38193</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.41539</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50432</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.29894</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35668</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.13641</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.14593</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.31038</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.25915</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>-0.00062</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.04901</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.56484</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>-0.02946</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>-0.00532</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.67722</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.6105700000000001</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>-0.03844</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.09073000000000001</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.80037</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.26697</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.1665</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.2576</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.26879</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.5755399999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.59416</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.74409</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.7550800000000001</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.16104</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.24754</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.1327</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.83794</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.20492</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.10588</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.25635</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.02265</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.09014</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.65097</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.98303</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.91369</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.95778</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.78142</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.8901</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.7385499999999999</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.77894</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.45116</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.72953</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.7621</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.45107</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.4298</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4452</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3331</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33493</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.51306</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.49306</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48979</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36741</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4449</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41554</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.39162</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38502</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36481</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43155</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44761</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33649</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37213</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.36898</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.36972</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.36306</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35321</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.37818</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.36519</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.39013</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47769</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4464</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44159</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.21898</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.31271</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.08120000000000001</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.35146</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.33302</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.43241</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.22176</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7811900000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.4811</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.26266</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.42268</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.43199</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.43341</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.42989</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5140800000000001</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.48586</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.44264</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.28459</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.62095</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.64458</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.46602</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.50602</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.4703</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.5506599999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.48916</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.61314</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.2991</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.48409</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.61742</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.57363</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.55759</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.7187100000000001</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.6033200000000001</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.51993</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.41907</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.55486</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.43427</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.4585</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39813</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34912</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34233</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.51515</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.5027900000000001</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.43924</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.39352</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.39254</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.39972</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36164</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.39271</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.39031</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36617</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.45229</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.36385</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.35126</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36782</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3624</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33723</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33373</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35158</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33986</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35251</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38932</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.35236</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37884</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.3458</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.39649</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.4201</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35837</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.40394</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.34402</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.10202</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.06715</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.1524</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.28143</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.06006</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.56288</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.17424</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.16253</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.13312</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3058</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.39823</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6234299999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34226</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.44563</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37727</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.40655</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.28186</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.41364</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.47542</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.44907</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.50913</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45113</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.4669</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.40205</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47493</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.48735</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.54998</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.55771</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.49376</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.46866</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50458</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.4265</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.40599</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.4012</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.4221</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.36365</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32349</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32068</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31825</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.32124</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34103</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38147</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33843</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32712</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31865</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31549</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31758</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31511</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.3107799999999999</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31215</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30901</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30844</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.3132</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33259</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.31464</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.28555</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.2865</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.30484</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.11121</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31898</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30383</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.27067</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.08137999999999999</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.2684</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.16012</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.1006</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.13261</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.10702</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04686999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.01767</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.17317</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.17246</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.05122</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>-0.00047</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.01017</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.01765</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.24166</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29662</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29918</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.3357</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.41983</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.4206</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.41844</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.43163</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.43704</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.48609</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.38644</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.41444</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.5456599999999999</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34596</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.37125</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.8542799999999999</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.46008</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.5695</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.5290900000000001</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.54216</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.40162</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.41757</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.33001</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.42952</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.41982</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.6054299999999999</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.3652</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.36624</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.35302</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.40355</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.37919</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.40759</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.32109</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.41142</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.35332</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10216</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04319</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04575</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04489</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.00558</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.19775</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04505</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.26294</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.15395</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04334</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04548</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04338</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.02904</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04537</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.0519</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05007</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19974</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30453</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29281</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29224</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30854</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35585</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.38282</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.37835</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.34723</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32338</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.43108</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32144</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30705</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27068</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31624</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42901</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45778</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41842</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39227</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.4024</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15655</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29425</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30066</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.62203</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78547</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92038</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49455</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9141900000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86286</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29619</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35361</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88746</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63159</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18705</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8691599999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.57378</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33081</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03289</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.5307500000000001</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79096</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.5418200000000001</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77295</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77752</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87385</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49312</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39865</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39985</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44991</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20696</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87882</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55101</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62181</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53831</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49768</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43713</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45042</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41998</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.36611</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40424</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.37226</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38921</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.45501</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.35586</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39955</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.33867</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.4554</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34743</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45497</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.37365</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.44704</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.6665099999999999</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.50204</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.62741</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.81396</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8840800000000001</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.47117</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.49537</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.66547</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.49801</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>1.04434</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.7993899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.87414</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87503</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.35547</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.5140800000000001</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.89998</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.3415899999999999</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.31392</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.32013</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.8346699999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.5906699999999999</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.35751</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.36886</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32083</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40649</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34588</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31989</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.36788</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.33307</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32471</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29597</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.3149</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.32503</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31618</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.39677</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.33879</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.34693</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.36049</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.35081</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.37233</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.3699</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.35826</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.35616</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.36084</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.47487</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.47894</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.53874</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.48255</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.44346</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.4261</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.37147</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.9357799999999999</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.5275599999999999</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.47487</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.45604</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.55041</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.42269</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.46826</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.38755</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.39686</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.37793</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.34858</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.39078</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.37253</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.46565</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.61152</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.38905</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.44239</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.37132</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.3902</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.41484</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.39887</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.34008</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.35481</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.36088</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.37521</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.32192</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.22397</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.2843</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.09295999999999999</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30407</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.3092200000000001</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30857</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.26648</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.29007</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20075</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.31149</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29898</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.28577</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.31493</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.31531</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.3591</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.37045</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.32636</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.33498</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.32925</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.3302</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.34162</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.30611</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.32768</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.29231</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.37735</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25853</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.34647</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.36085</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27961</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.38834</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.36989</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.38256</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.35893</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.4307</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.5322</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.36882</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.37002</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.37246</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.47368</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.36841</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.4757</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.3789</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.4616</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.46326</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.77964</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.43097</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.9464900000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.48259</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.20162</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.72942</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.82133</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.68057</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.7989700000000001</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.5940299999999999</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.47572</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.5267500000000001</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.46441</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.49656</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.43964</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.43527</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.47748</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.61212</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.43491</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.45718</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.48305</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.45669</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.40944</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.5122899999999999</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.5477300000000001</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.44452</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.5202100000000001</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.43486</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.43131</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.46714</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.50975</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.47319</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.5169</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.45704</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.42821</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.40557</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.32517</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.6289600000000001</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.38301</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.5542899999999999</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.25166</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.32782</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15726</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.29005</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01695</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30145</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.26433</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25891</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30928</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28451</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29641</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30098</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.29861</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.3211</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.33806</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.35416</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.37083</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.36897</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.4491</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.44667</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.36895</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.35915</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.37575</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.39075</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.41294</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.39435</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.38317</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.36957</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.6511</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>1.01811</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.55331</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.52025</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.41738</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.51029</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.42999</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.40498</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.35861</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.38523</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3527</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.36901</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.51686</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.39175</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.4489</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.35278</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.41065</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.41322</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.41487</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.4077</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.42818</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.37353</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.37257</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.33905</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.3351</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.42532</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.33133</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.33052</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.5376000000000001</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.40642</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.51328</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.548</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.52686</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.49355</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.40159</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.35817</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.42731</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.36941</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.36081</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.40877</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.30728</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.32313</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.21497</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.07457</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.10065</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28306</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.1173</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.0861</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.09320000000000001</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.26474</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.10394</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.23094</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.08904999999999999</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.25615</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.29438</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.13053</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05578</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.03257</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.06681999999999999</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.05948</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.163</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.07792</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28894</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.3742200000000001</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.3469100000000001</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.39145</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.39058</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.42651</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.42538</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.37342</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.45429</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.40115</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.43875</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.54267</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.46277</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.44594</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.46576</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.45614</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.54208</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.52832</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.52438</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.53091</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.46189</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.42202</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.40986</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.4163</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.41004</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.4045899999999999</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.40406</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.40715</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.38964</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.36911</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.6767300000000001</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.40672</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.56498</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.49359</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.48204</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.41379</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.42985</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.42675</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.44556</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.39761</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.42408</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.39377</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.44241</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.41079</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.43075</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.37501</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.37538</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.5412899999999999</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.42912</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.39699</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.36408</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.34835</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.36705</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.31454</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.31433</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.30191</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.26571</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.23728</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.17569</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.21577</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.18713</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30086</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30054</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.23169</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28534</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29318</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.2697</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.25669</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.32849</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.3213</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.34259</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.35818</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.33508</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.46842</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.40479</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.36577</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.35944</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.36815</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.36964</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3643</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.37909</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.40784</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.51912</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.41904</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.32939</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.37993</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.38975</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.47216</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.36345</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.36909</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.39715</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.40035</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.38563</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.43677</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.42404</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.43082</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.37753</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.39381</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.35249</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.40124</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.62997</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.38866</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.63759</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.42245</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.38229</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.42036</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.40083</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.39129</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.37183</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.38053</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.37496</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.38006</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.36482</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.38324</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.35651</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.36545</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.35781</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.35312</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.36884</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.37009</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.383</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.43505</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.39805</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.41894</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.41225</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.39936</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.45232</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.1375</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.43251</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.6786799999999999</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.37331</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.51455</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.4635</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.36641</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.40501</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.46314</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.32035</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.42111</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.42278</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.25855</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.2683</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.18099</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.14172</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28128</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.24692</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.56113</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.34215</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.3531</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.29127</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.42756</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.34419</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.09916</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.35191</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.4255</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.39811</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.36878</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.37199</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.34285</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.43458</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.58229</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.48012</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.4654</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.4469</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.7189</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38957</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>1.0465</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.89249</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.72157</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.39295</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.5279700000000001</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.26895</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.40838</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36301</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.34459</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.36865</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.38507</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.66023</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.42268</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32005</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.51459</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.42728</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.38757</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.38968</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.42416</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.43266</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.405</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.36728</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.38042</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.36353</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.36506</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.36361</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.35912</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.41217</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.34278</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.41701</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.4314</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.3728399999999999</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.36564</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.41674</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.42064</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.42757</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.4411600000000001</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.46296</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.44305</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.4342</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.38738</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.37394</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.3986</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.35345</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.43126</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.36554</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.34006</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.36597</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.35791</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.3355</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.36474</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.30213</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.36273</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.34527</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.34489</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.34754</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.35333</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.36988</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.35815</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.35474</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.34532</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.40628</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.38588</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.32368</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.38898</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.40709</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.37077</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.3714</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.37383</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.37235</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.38087</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.41605</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.3654</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.42895</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.38705</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.37896</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.42257</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.38014</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.45806</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.44483</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.39025</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.5039399999999999</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.37381</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.44229</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.38731</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.45528</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.4645</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.41966</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.36799</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.36839</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.3687</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36771</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.36967</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.36916</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.39148</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.3677</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.36456</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.58999</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.38594</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.38861</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.37266</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.42196</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.3579</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.38976</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.38037</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.36336</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.386</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.38631</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.35464</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.37669</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.36149</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.38803</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.3696</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.36711</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.36843</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.33212</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.3435</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.32913</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32938</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37049</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.34173</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.32289</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.33789</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32421</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32857</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.36368</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.34804</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.36002</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.3821</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.36071</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.3726</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.37795</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.38589</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.3682</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.38715</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.36632</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.38542</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.37709</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.36704</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.41571</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.42841</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.4204</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.42132</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.48941</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39412</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.6743400000000001</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.07025</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.5216000000000001</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.37249</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.54411</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.36868</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.36851</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.3772799999999999</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3577</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.42994</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.39508</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.37765</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.38082</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.38865</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.37164</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.37879</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.39051</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.37492</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.37088</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.38945</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.3782799999999999</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.37861</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.36633</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.42529</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.37757</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.37531</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.42321</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.38468</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.37537</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.36998</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.37671</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.36921</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.34357</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.3583</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.37898</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.2608</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.1094</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.30456</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.19514</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.12901</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.21237</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.24356</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.24536</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.25323</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.15684</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.21868</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.2596</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.24985</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.29077</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.27625</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.29928</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33053</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.40926</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.28226</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.2913</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.35704</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.35294</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.36168</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.38896</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.34334</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.37592</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.42589</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.46751</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.5611499999999999</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.5024</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.46761</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.67943</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.63701</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.65464</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.64335</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.8472499999999999</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.6172799999999999</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.18573</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.66351</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.52318</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.43488</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.42071</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.45835</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.60193</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.50192</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.48362</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.41525</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.39355</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.39906</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.38895</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34564</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.5885499999999999</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.7234400000000001</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.62906</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.90008</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.47676</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.47853</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.4542</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.46841</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.46193</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.47662</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.44712</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.41308</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.45547</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.43561</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.4865</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.43686</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.48357</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.4407799999999999</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.47023</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.46023</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.47616</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.46514</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.5557300000000001</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.54406</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.72615</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.6205000000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.5376799999999999</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.60977</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.5338099999999999</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.46499</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.38397</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.41261</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.4311</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.46775</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.46833</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.5484600000000001</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.45297</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.41798</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.37474</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.38934</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.4689</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.43157</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.37054</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.37664</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.29742</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.32717</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.31821</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.39694</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.6474299999999999</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.6694099999999999</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.30889</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.24823</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.382</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.41283</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33844</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.37195</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.36459</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.40806</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.4153</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.41807</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.4369</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.35602</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.47039</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.50641</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.59536</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.53473</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.6338200000000001</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.6361100000000001</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.70137</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.94298</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.16723</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.28356</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.9256599999999999</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>1.09459</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.91242</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.69225</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>1.13708</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.78788</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.6414099999999999</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.69072</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.55865</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.5879500000000001</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.5853200000000001</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.57372</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.56547</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.4764</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.69155</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.49428</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.51689</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.54138</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.45279</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.44274</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.52647</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.43446</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.45263</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.57257</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.46637</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.47529</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.43452</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.41771</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.41543</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.37855</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.37535</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.61187</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.43048</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.40754</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.37821</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.38432</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.45495</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.45683</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.41277</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.37974</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.39787</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.40883</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.40415</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.41792</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.44056</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.40509</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35163</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.39778</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.3613</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.35953</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.39855</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.26124</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.40722</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.21516</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.00618</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35401</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.43944</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.36619</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.3706</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40296</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.5149199999999999</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.38759</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01383</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.10833</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.0372</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.29078</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.32331</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.37617</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.38171</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.43015</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.44357</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.4887</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.46693</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.45378</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.4358399999999999</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.5209400000000001</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.4264</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.46546</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.48981</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.50061</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.5165</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.49515</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.46268</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.39538</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.47324</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.43236</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.38011</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.46963</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.50619</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.42504</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.48052</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.52388</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.50462</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.46321</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.41819</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.6212300000000001</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.47491</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.49026</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.49545</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.4577</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.47879</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.46456</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.61654</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.5861900000000001</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.58035</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.46418</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.5938</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.43712</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.36982</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.46358</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.5557300000000001</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.44004</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.45127</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.43001</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.44519</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.45162</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.45805</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.5407000000000001</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.46448</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.5389299999999999</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.55462</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.49024</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.40251</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.4207</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.55438</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.36874</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.38336</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.35157</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.34959</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.1826</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.32092</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.21038</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.21239</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.28141</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.35175</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.31265</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.42914</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.23012</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.06994</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.29755</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.27052</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.09201000000000001</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.11121</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.29562</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.3131</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.18428</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.22422</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.27312</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.2148</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27656</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28574</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.36912</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.35728</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.38979</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.37889</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.37151</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.4223</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.43307</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.44537</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.45855</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.40111</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.33051</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.45148</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.40963</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.44917</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.415</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.47136</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.49484</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.46855</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42275</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.4416</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.4384</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.3963</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.43238</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.48515</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.50015</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.40385</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.4596</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.39119</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.46025</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.42297</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.37694</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.38194</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.3787</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.3781600000000001</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.37799</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.50992</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.40674</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.40075</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.34784</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.50183</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.37375</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.36764</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.36819</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.47564</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.5125</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.50403</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.50156</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.50501</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.49787</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.49848</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.39095</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.5127999999999999</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.51237</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.51602</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.2938</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.0331</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00091</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.1514</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02276</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03959</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.0149</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04308</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04103</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04864</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.0483</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02445</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02947</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.03788</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04942</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>0.00147</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27906</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03629</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01509</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04966</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03559</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20556</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26885</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.29222</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.3336</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.50892</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.33899</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.3676</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.37142</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.36433</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.3974</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.38982</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.39768</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.36836</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.38807</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.42024</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.5364800000000001</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.39153</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.42735</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.38862</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.38808</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.38782</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.38609</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.38831</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.40756</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>1.17365</v>
+      </c>
+      <c r="D137" t="n">
+        <v>1.00657</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.49036</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.86303</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.52222</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.53711</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.58992</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.44865</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.50422</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.36881</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.46621</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.47923</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.47365</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.62686</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.46047</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.43447</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.649</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.56063</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.63986</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.58613</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.6422100000000001</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.60999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.5939800000000001</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.61846</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.65974</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.46475</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.53337</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.41249</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.37388</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.5841900000000001</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.5172100000000001</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>1.48117</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>1.3913</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.91001</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8722799999999999</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.41515</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.00549</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.10146</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.006480000000000001</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.03129</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.01582</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.00521</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.05391</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.00051</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.04595</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>-0.03354</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.04077</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.30234</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>-0.0294</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.03265</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30579</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.01891</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.31297</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25442</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29183</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.39713</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.36531</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.42472</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.44475</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.37409</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.40907</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.4463</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.02918</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.12927</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.09129</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.99921</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.11631</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.03398</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>1.12554</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.86153</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.8597899999999999</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.86393</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.96077</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>1.11811</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>1.12152</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>1.11296</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.40054</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.39136</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.39567</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.41868</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.41852</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.59613</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.8753099999999999</v>
+      </c>
+      <c r="E138" t="n">
+        <v>1.41723</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.822</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.51732</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.61356</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.51213</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.51178</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.40454</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.47962</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.5199600000000001</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.40614</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.41985</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.40469</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.4222</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.65442</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.43901</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.46251</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.42941</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.44982</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.45502</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.59899</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.52461</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.4969</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.49681</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.65991</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.4885</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.51501</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.34482</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.3946</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.38702</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.22055</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.40185</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.05875</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.37858</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.31119</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.11122</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>-0.02356</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>-0.0185</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.01036</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.09770999999999999</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.22596</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.27136</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.26094</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31321</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32228</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.32006</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31548</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.35094</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.33371</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33658</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32497</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.3602</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.36314</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.3769</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.3865</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.41642</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.41181</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.41371</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.4496</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.61905</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.2137</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.50125</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.89506</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.6039</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.44447</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.5402400000000001</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.5311</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.48319</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.66414</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.4054</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.39786</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.40864</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.39961</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.49344</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.50952</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4804</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.47366</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.4511</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.44525</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.43935</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.41437</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.40481</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.40499</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.37217</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3962</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.38824</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.36772</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.40495</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.38185</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.38059</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.37627</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.3766600000000001</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.37714</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.37721</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.39264</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.40392</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.39387</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.40465</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.38841</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.40245</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.54026</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.43309</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.84028</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.9983300000000001</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.8208099999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.25599</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.76219</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.58741</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.40595</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.38619</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.36477</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.37446</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.37848</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.41385</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.36933</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.31208</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.36023</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.34399</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.29793</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.34951</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32557</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32292</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.30639</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.36568</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.35972</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42526</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3922</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.41048</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.9608</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.8301900000000001</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.46357</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.46356</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.5722</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.55565</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.64432</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.8169999999999999</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.56463</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.91199</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.79365</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.6027899999999999</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.60526</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.43697</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.4599</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.5313600000000001</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.41148</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.37864</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.53291</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.44514</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.39651</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.44477</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.27985</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.40488</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.39223</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.40005</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.36411</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.52571</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.43936</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.44727</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.41293</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.39158</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.41401</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.41232</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.40446</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.39605</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.38777</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.3866</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.38781</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.38753</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.38761</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.37877</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.3799</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.36682</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.40143</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.41033</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.45573</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.41869</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3828</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.38385</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.37566</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.38876</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.40635</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39063</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.39147</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35337</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43415</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37929</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.38813</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.39288</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.38099</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31039</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.28804</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.3987</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.38408</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.37726</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29265</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.33768</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.3139</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.3164</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34376</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32534</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33334</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34128</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33778</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32478</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.3441</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34934</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.40832</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.39693</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.36522</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.40645</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.43094</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.39884</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41071</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.44377</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.45212</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.3508</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.50534</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.66315</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.39371</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.68335</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.77113</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.54172</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.41885</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.76812</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47697</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.5905900000000001</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.9349299999999999</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.5237999999999999</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.5108199999999999</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.52407</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>1.00183</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.47472</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.49154</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.43528</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.40194</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.40493</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.40424</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.3212</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.39407</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.38665</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.4003</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.37668</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.36665</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.39862</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.39234</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.36932</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.45571</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.37068</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.39519</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.38801</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.60327</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.37908</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.3838</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.36655</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.36142</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.37519</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.42264</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.40306</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.40455</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.38234</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3936</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.39026</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.37767</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.44336</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.35774</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.39083</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.33724</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.17727</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.27184</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.28996</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.17441</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.3279</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.20758</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.09673999999999999</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.18846</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.009609999999999999</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.05639</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.29491</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.26496</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.0132</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.04031000000000001</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.04457</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.11087</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.03295</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.00519</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2935</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.23253</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.18321</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.20817</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.35542</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.32251</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.43554</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.40104</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.38717</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.39205</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.3739</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.40249</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.41993</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.54288</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.4391600000000001</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.45668</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.51766</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.47324</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.42508</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.42382</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.41144</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.42475</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.44535</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.38877</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.47837</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.4074</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.39945</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.40232</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.393</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.41779</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3432</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.25152</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.43431</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.21639</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.46021</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.43259</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.40502</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.29836</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.42247</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.41489</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.40955</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.40526</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.40387</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.40045</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.41608</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.40561</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.406</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.3999</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.39734</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.39929</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.39548</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.39446</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.38993</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.3954</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.3886</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.41025</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.38758</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.37245</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.38428</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.38953</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.39402</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.39523</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.38443</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.35611</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.39586</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.34494</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.34094</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.23132</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.26583</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33089</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.28052</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.2862</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.33752</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.09523999999999999</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.29208</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.12886</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.38409</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.2753</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32597</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35091</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.33206</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.31161</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.41504</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.41089</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42028</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.42454</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.43143</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.37494</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.39225</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40577</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.40913</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.37363</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.43269</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.40654</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.41478</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39752</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.41383</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.42445</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.38431</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.39518</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.41096</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.40961</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.41827</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.38835</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34872</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.41159</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.45243</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.373</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.4031</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.40283</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.40496</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.40428</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.39621</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.38696</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.40671</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.38122</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.39964</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.3976</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.39141</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.38999</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.38564</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.38744</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.39032</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.38533</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.36144</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3901</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3792</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.38173</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.32624</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.32025</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.32499</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17683</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30249</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31326</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14646</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19968</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>-0.01783</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.24396</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>-0.03172</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>-0.02128</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.00557</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>-0.01141</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>-0.01329</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.13336</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.02265</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.07224</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.17656</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>-0.00118</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.22763</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.26739</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15519</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.26142</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.31045</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>-0.0167</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.22637</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.04835</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20007</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.14772</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.25862</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.29493</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.30523</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32622</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.34294</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.36499</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.4152</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.36775</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.37969</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.39308</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37168</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.39365</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.4283</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.42005</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.4166</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.42672</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.40741</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.40601</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.43058</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.50904</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.39732</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41644</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.41919</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41596</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.3825</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.40337</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.40931</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.40789</v>
       </c>
     </row>
   </sheetData>
